--- a/tests/ITER_coil_inf_3D/input_template.xlsx
+++ b/tests/ITER_coil_inf_3D/input_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlasmaArc\simulations\ITER_coil_inf_3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlasmaArc\tests\ITER_coil_inf_3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B9D368-7691-4623-A099-10315F6D4DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897EC1CC-DA66-4CED-9338-703AF65CEFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="element_types" sheetId="1" r:id="rId1"/>
@@ -1468,7 +1468,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
@@ -1545,6 +1545,77 @@
       </c>
       <c r="W1" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/ITER_coil_inf_3D/input_template.xlsx
+++ b/tests/ITER_coil_inf_3D/input_template.xlsx
@@ -1,29 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlasmaArc\tests\ITER_coil_inf_3D\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C37DCAC-CC36-4751-BA6F-1CB196CE327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="element_types"/>
-    <sheet r:id="rId2" sheetId="2" name="cp"/>
-    <sheet r:id="rId3" sheetId="3" name="cpcyc"/>
-    <sheet r:id="rId4" sheetId="4" name="materials"/>
-    <sheet r:id="rId5" sheetId="5" name="real_constants"/>
-    <sheet r:id="rId6" sheetId="6" name="solver_settings"/>
-    <sheet r:id="rId7" sheetId="7" name="time_parameters"/>
-    <sheet r:id="rId8" sheetId="8" name="elem"/>
-    <sheet r:id="rId9" sheetId="9" name="node"/>
-    <sheet r:id="rId10" sheetId="10" name="transient_analysis"/>
+    <sheet name="element_types" sheetId="1" r:id="rId1"/>
+    <sheet name="cp" sheetId="2" r:id="rId2"/>
+    <sheet name="cpcyc" sheetId="3" r:id="rId3"/>
+    <sheet name="materials" sheetId="4" r:id="rId4"/>
+    <sheet name="real_constants" sheetId="5" r:id="rId5"/>
+    <sheet name="solver_settings" sheetId="6" r:id="rId6"/>
+    <sheet name="time_parameters" sheetId="7" r:id="rId7"/>
+    <sheet name="elem" sheetId="8" r:id="rId8"/>
+    <sheet name="node" sheetId="9" r:id="rId9"/>
+    <sheet name="transient_analysis" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="113">
   <si>
     <t>time_step_number</t>
   </si>
@@ -205,21 +211,6 @@
     <t>ansys_real_constant</t>
   </si>
   <si>
-    <t>CARE</t>
-  </si>
-  <si>
-    <t>TURN</t>
-  </si>
-  <si>
-    <t>LENG</t>
-  </si>
-  <si>
-    <t>DIRZ</t>
-  </si>
-  <si>
-    <t>FILL</t>
-  </si>
-  <si>
     <t>SC</t>
   </si>
   <si>
@@ -368,12 +359,21 @@
   </si>
   <si>
     <t>INFIN111</t>
+  </si>
+  <si>
+    <t>THK</t>
+  </si>
+  <si>
+    <t>VC</t>
+  </si>
+  <si>
+    <t>CPSIGN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
@@ -426,74 +426,65 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -504,10 +495,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -545,71 +536,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -637,7 +628,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -660,11 +651,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -673,13 +664,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -689,7 +680,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -698,7 +689,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -707,7 +698,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -715,10 +706,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -783,120 +774,116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="14.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5">
-        <v>21</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5">
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="4">
         <v>3</v>
       </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="4">
         <v>4</v>
       </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>111</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>114</v>
+      <c r="B5" t="s">
+        <v>109</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -907,10 +894,10 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
         <v>0</v>
       </c>
     </row>
@@ -920,24 +907,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="18.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="22.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="16.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="21.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="21.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -947,253 +934,253 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6">
-        <v>0.0001</v>
-      </c>
-      <c r="C2" s="5">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1E-4</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.75</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
-        <v>0.0002</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B3" s="5">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="C3" s="4">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6">
         <v>0.75</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
-        <v>0.0003</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="5">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="C4" s="4">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6">
         <v>0.75</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="5">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
-        <v>0.0004</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="5">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6">
         <v>0.75</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="5">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
-        <v>0.0005</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="5">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C6" s="4">
         <v>4</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6">
         <v>0.75</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="5">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
-        <v>0.001</v>
+      <c r="B7" s="5">
+        <v>1E-3</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="5">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6">
         <v>0.8</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="5">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="8">
-        <v>0.003</v>
+      <c r="B9" s="7">
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>0.8</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="5">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6">
         <v>0.9</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1203,57 +1190,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1261,68 +1233,57 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="14" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="7.147857142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="G1" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="H1" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="I1" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="J1" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+    </row>
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1330,189 +1291,178 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="20.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="20.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="13.5703125" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="H1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="I1" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="J1" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="K1" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="L1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="M1" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5">
+    </row>
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>21</v>
       </c>
-      <c r="B2" s="16">
-        <v>1.1</v>
-      </c>
-      <c r="C2" s="16">
+      <c r="B2" s="13">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C2" s="13">
         <v>1.2</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="13">
         <v>1.3</v>
       </c>
-      <c r="E2" s="16">
-        <v>0</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0</v>
-      </c>
-      <c r="H2" s="16">
-        <v>0</v>
-      </c>
-      <c r="I2" s="16">
-        <v>0</v>
-      </c>
-      <c r="J2" s="16">
-        <v>0</v>
-      </c>
-      <c r="K2" s="16">
-        <v>0</v>
-      </c>
-      <c r="L2" s="16">
-        <v>0</v>
-      </c>
-      <c r="M2" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5">
+      <c r="E2" s="13">
+        <v>0</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13">
+        <v>0</v>
+      </c>
+      <c r="I2" s="13">
+        <v>0</v>
+      </c>
+      <c r="J2" s="13">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13">
+        <v>0</v>
+      </c>
+      <c r="L2" s="13">
+        <v>0</v>
+      </c>
+      <c r="M2" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>23</v>
       </c>
-      <c r="B3" s="16">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16">
-        <v>1</v>
-      </c>
-      <c r="D3" s="16">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16">
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
-        <v>0</v>
-      </c>
-      <c r="G3" s="16">
-        <v>0</v>
-      </c>
-      <c r="H3" s="16">
-        <v>0</v>
-      </c>
-      <c r="I3" s="16">
-        <v>0</v>
-      </c>
-      <c r="J3" s="16">
-        <v>0</v>
-      </c>
-      <c r="K3" s="16">
-        <v>0</v>
-      </c>
-      <c r="L3" s="16">
-        <v>0</v>
-      </c>
-      <c r="M3" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5">
+      <c r="B3" s="13">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13">
+        <v>1</v>
+      </c>
+      <c r="D3" s="13">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13">
+        <v>0</v>
+      </c>
+      <c r="G3" s="13">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13">
+        <v>0</v>
+      </c>
+      <c r="I3" s="13">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13">
+        <v>0</v>
+      </c>
+      <c r="M3" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>24</v>
       </c>
-      <c r="B4" s="16">
-        <v>1</v>
-      </c>
-      <c r="C4" s="16">
-        <v>1</v>
-      </c>
-      <c r="D4" s="16">
-        <v>1</v>
-      </c>
-      <c r="E4" s="16">
-        <v>5e-9</v>
-      </c>
-      <c r="F4" s="16">
-        <v>5e-9</v>
-      </c>
-      <c r="G4" s="16">
-        <v>5e-9</v>
-      </c>
-      <c r="H4" s="16">
-        <v>0</v>
-      </c>
-      <c r="I4" s="16">
-        <v>0</v>
-      </c>
-      <c r="J4" s="16">
-        <v>0</v>
-      </c>
-      <c r="K4" s="16">
-        <v>0</v>
-      </c>
-      <c r="L4" s="16">
-        <v>0</v>
-      </c>
-      <c r="M4" s="16">
+      <c r="B4" s="13">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13">
+        <v>1</v>
+      </c>
+      <c r="D4" s="13">
+        <v>1</v>
+      </c>
+      <c r="E4" s="13">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="F4" s="13">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="G4" s="13">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0</v>
+      </c>
+      <c r="I4" s="13">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1522,110 +1472,84 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="9" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="21.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="G1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="H1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="I1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="J1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="K1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="L1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="M1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="N1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="O1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="P1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="Q1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="R1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="S1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="T1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="T1" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="U1" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="V1" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="W1" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="U1" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1687,12 +1611,6 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
-        <v>0</v>
-      </c>
-      <c r="V2" s="1">
-        <v>0</v>
-      </c>
-      <c r="W2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1702,279 +1620,279 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="34.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="18" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="16">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="13">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="16">
-        <v>1e-10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="13">
+        <v>1E-10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="16">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
+      <c r="B9" s="13">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
+      <c r="B10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="16">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
+      <c r="B12" s="13">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="16">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3" t="s">
+      <c r="B15" s="13">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="16">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3" t="s">
+      <c r="B16" s="13">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="3" t="s">
+      <c r="B17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="3" t="s">
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="3" t="s">
+      <c r="B19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="3" t="s">
+      <c r="B21" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="3" t="s">
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="3" t="s">
+      <c r="B23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="3" t="s">
+      <c r="B24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="3" t="s">
+      <c r="B25" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="3" t="s">
+      <c r="B26" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="3" t="s">
+      <c r="B27" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="3" t="s">
+      <c r="B28" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="3" t="s">
+      <c r="B29" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="3" t="s">
+      <c r="B30" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="3" t="s">
+      <c r="B31" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="3" t="s">
+      <c r="B32" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="16">
-        <v>0.000001</v>
+      <c r="B33" s="13">
+        <v>9.9999999999999995E-7</v>
       </c>
     </row>
   </sheetData>
@@ -1983,78 +1901,78 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="23.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>1</v>
       </c>
     </row>
@@ -2064,80 +1982,72 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="14" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="15"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="15"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="15"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="15"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="15"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="15"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="15"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="15"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2145,110 +2055,97 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="14" width="16.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="17.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="12.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="16.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="5"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="5"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="5"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="5"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="5"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="5"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="5"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="5"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="5"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/ITER_coil_inf_3D/input_template.xlsx
+++ b/tests/ITER_coil_inf_3D/input_template.xlsx
@@ -1,30 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlasmaArc\tests\ITER_coil_inf_3D\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C37DCAC-CC36-4751-BA6F-1CB196CE327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="element_types" sheetId="1" r:id="rId1"/>
-    <sheet name="cp" sheetId="2" r:id="rId2"/>
-    <sheet name="cpcyc" sheetId="3" r:id="rId3"/>
-    <sheet name="materials" sheetId="4" r:id="rId4"/>
-    <sheet name="real_constants" sheetId="5" r:id="rId5"/>
-    <sheet name="solver_settings" sheetId="6" r:id="rId6"/>
-    <sheet name="time_parameters" sheetId="7" r:id="rId7"/>
-    <sheet name="elem" sheetId="8" r:id="rId8"/>
-    <sheet name="node" sheetId="9" r:id="rId9"/>
-    <sheet name="transient_analysis" sheetId="10" r:id="rId10"/>
+    <sheet r:id="rId1" sheetId="1" name="element_types"/>
+    <sheet r:id="rId2" sheetId="2" name="cp"/>
+    <sheet r:id="rId3" sheetId="3" name="cpcyc"/>
+    <sheet r:id="rId4" sheetId="4" name="materials"/>
+    <sheet r:id="rId5" sheetId="5" name="real_constants"/>
+    <sheet r:id="rId6" sheetId="6" name="solver_settings"/>
+    <sheet r:id="rId7" sheetId="7" name="time_parameters"/>
+    <sheet r:id="rId8" sheetId="8" name="elem"/>
+    <sheet r:id="rId9" sheetId="9" name="node"/>
+    <sheet r:id="rId10" sheetId="10" name="transient_analysis"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -211,12 +205,18 @@
     <t>ansys_real_constant</t>
   </si>
   <si>
+    <t>THK</t>
+  </si>
+  <si>
     <t>SC</t>
   </si>
   <si>
     <t>NC</t>
   </si>
   <si>
+    <t>VC</t>
+  </si>
+  <si>
     <t>RAD</t>
   </si>
   <si>
@@ -262,6 +262,9 @@
     <t>ZLOC</t>
   </si>
   <si>
+    <t>CPSIGN</t>
+  </si>
+  <si>
     <t>ansys_material_type</t>
   </si>
   <si>
@@ -359,21 +362,12 @@
   </si>
   <si>
     <t>INFIN111</t>
-  </si>
-  <si>
-    <t>THK</t>
-  </si>
-  <si>
-    <t>VC</t>
-  </si>
-  <si>
-    <t>CPSIGN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
@@ -388,13 +382,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -426,65 +420,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="15">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -495,10 +483,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -536,71 +524,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -628,7 +616,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -651,11 +639,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -664,13 +652,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -680,7 +668,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -689,7 +677,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -698,7 +686,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -706,10 +694,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -774,116 +762,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="14.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" t="s">
-        <v>102</v>
+        <v>104</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+        <v>110</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="B2" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="1">
         <v>3</v>
       </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="B4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1">
         <v>111</v>
       </c>
-      <c r="B5" t="s">
-        <v>109</v>
+      <c r="B5" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -894,10 +886,10 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -907,24 +899,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="22.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="16.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="21.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="21.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -934,253 +926,253 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>1E-4</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+        <v>0.0001</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5">
         <v>0.75</v>
       </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="C3" s="4">
+        <v>0.0002</v>
+      </c>
+      <c r="C3" s="1">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5">
         <v>0.75</v>
       </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="C4" s="4">
+        <v>0.0003</v>
+      </c>
+      <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5">
         <v>0.75</v>
       </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="C5" s="4">
+        <v>0.0004</v>
+      </c>
+      <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5">
         <v>0.75</v>
       </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="5">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="C6" s="4">
+        <v>0.0005</v>
+      </c>
+      <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="5">
         <v>0.75</v>
       </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="G6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="5">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="6">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="5">
         <v>0.8</v>
       </c>
-      <c r="G8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="G8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="7">
-        <v>3.0000000000000001E-3</v>
+      <c r="B9" s="2">
+        <v>0.003</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>0.8</v>
       </c>
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="5">
         <v>0.9</v>
       </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="G10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1190,42 +1182,57 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
+      <c r="D1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1233,57 +1240,68 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="11" width="14.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="7.147857142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I1" t="s">
         <v>98</v>
       </c>
-      <c r="J1" t="s">
+      <c r="G1" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+      <c r="H1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1291,178 +1309,189 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="13.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="20.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="I1" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="J1" s="12" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="K1" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" s="13">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="12">
+        <v>1.1</v>
+      </c>
+      <c r="C2" s="12">
         <v>1.2</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>1.3</v>
       </c>
-      <c r="E2" s="13">
-        <v>0</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0</v>
-      </c>
-      <c r="I2" s="13">
-        <v>0</v>
-      </c>
-      <c r="J2" s="13">
-        <v>0</v>
-      </c>
-      <c r="K2" s="13">
-        <v>0</v>
-      </c>
-      <c r="L2" s="13">
-        <v>0</v>
-      </c>
-      <c r="M2" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="E2" s="12">
+        <v>0</v>
+      </c>
+      <c r="F2" s="12">
+        <v>0</v>
+      </c>
+      <c r="G2" s="12">
+        <v>0</v>
+      </c>
+      <c r="H2" s="12">
+        <v>0</v>
+      </c>
+      <c r="I2" s="12">
+        <v>0</v>
+      </c>
+      <c r="J2" s="12">
+        <v>0</v>
+      </c>
+      <c r="K2" s="12">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12">
+        <v>0</v>
+      </c>
+      <c r="M2" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" s="13">
-        <v>1</v>
-      </c>
-      <c r="C3" s="13">
-        <v>1</v>
-      </c>
-      <c r="D3" s="13">
-        <v>1</v>
-      </c>
-      <c r="E3" s="13">
-        <v>0</v>
-      </c>
-      <c r="F3" s="13">
-        <v>0</v>
-      </c>
-      <c r="G3" s="13">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13">
-        <v>0</v>
-      </c>
-      <c r="I3" s="13">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13">
-        <v>0</v>
-      </c>
-      <c r="K3" s="13">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13">
-        <v>0</v>
-      </c>
-      <c r="M3" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="B3" s="12">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1</v>
+      </c>
+      <c r="D3" s="12">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0</v>
+      </c>
+      <c r="K3" s="12">
+        <v>0</v>
+      </c>
+      <c r="L3" s="12">
+        <v>0</v>
+      </c>
+      <c r="M3" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="13">
-        <v>1</v>
-      </c>
-      <c r="C4" s="13">
-        <v>1</v>
-      </c>
-      <c r="D4" s="13">
-        <v>1</v>
-      </c>
-      <c r="E4" s="13">
-        <v>5.0000000000000001E-9</v>
-      </c>
-      <c r="F4" s="13">
-        <v>5.0000000000000001E-9</v>
-      </c>
-      <c r="G4" s="13">
-        <v>5.0000000000000001E-9</v>
-      </c>
-      <c r="H4" s="13">
-        <v>0</v>
-      </c>
-      <c r="I4" s="13">
-        <v>0</v>
-      </c>
-      <c r="J4" s="13">
-        <v>0</v>
-      </c>
-      <c r="K4" s="13">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13">
-        <v>0</v>
-      </c>
-      <c r="M4" s="13">
+      <c r="B4" s="12">
+        <v>1</v>
+      </c>
+      <c r="C4" s="12">
+        <v>1</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12">
+        <v>5e-9</v>
+      </c>
+      <c r="F4" s="12">
+        <v>5e-9</v>
+      </c>
+      <c r="G4" s="12">
+        <v>5e-9</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0</v>
+      </c>
+      <c r="K4" s="12">
+        <v>0</v>
+      </c>
+      <c r="L4" s="12">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1472,84 +1501,102 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="6.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="D1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="E1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="F1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="G1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="H1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="I1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="J1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="K1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="L1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="M1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="N1" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="O1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="P1" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="Q1" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="R1" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="U1" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S1" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="T1" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="U1" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1620,279 +1667,279 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="8" width="34.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="12.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="13">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B4" s="12">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="13">
-        <v>1E-10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B6" s="12">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="13">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B9" s="12">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="13">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B12" s="12">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="13">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B15" s="12">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="13">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B16" s="12">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="13">
-        <v>9.9999999999999995E-7</v>
+      <c r="B33" s="12">
+        <v>0.000001</v>
       </c>
     </row>
   </sheetData>
@@ -1901,78 +1948,78 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="8" width="23.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="11.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="13">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
     </row>
@@ -1982,24 +2029,24 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="11" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C1" s="10" t="s">
@@ -2009,45 +2056,53 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="10"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="10"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="10"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="10"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="10"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="10"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="10"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="10"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2055,24 +2110,24 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="11" width="16.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="17.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C1" s="10" t="s">
@@ -2082,70 +2137,83 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/ITER_coil_inf_3D/input_template.xlsx
+++ b/tests/ITER_coil_inf_3D/input_template.xlsx
@@ -1,24 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APEC-M\tests\ITER_coil_inf_3D\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A99B08-2FDA-4329-A8D0-F97A86FA32A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="element_types"/>
-    <sheet r:id="rId2" sheetId="2" name="cp"/>
-    <sheet r:id="rId3" sheetId="3" name="cpcyc"/>
-    <sheet r:id="rId4" sheetId="4" name="materials"/>
-    <sheet r:id="rId5" sheetId="5" name="real_constants"/>
-    <sheet r:id="rId6" sheetId="6" name="solver_settings"/>
-    <sheet r:id="rId7" sheetId="7" name="time_parameters"/>
-    <sheet r:id="rId8" sheetId="8" name="elem"/>
-    <sheet r:id="rId9" sheetId="9" name="node"/>
-    <sheet r:id="rId10" sheetId="10" name="transient_analysis"/>
+    <sheet name="element_types" sheetId="1" r:id="rId1"/>
+    <sheet name="cp" sheetId="2" r:id="rId2"/>
+    <sheet name="cpcyc" sheetId="3" r:id="rId3"/>
+    <sheet name="materials" sheetId="4" r:id="rId4"/>
+    <sheet name="real_constants" sheetId="5" r:id="rId5"/>
+    <sheet name="solver_settings" sheetId="6" r:id="rId6"/>
+    <sheet name="time_parameters" sheetId="7" r:id="rId7"/>
+    <sheet name="elem" sheetId="8" r:id="rId8"/>
+    <sheet name="node" sheetId="9" r:id="rId9"/>
+    <sheet name="transient_analysis" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -367,7 +373,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
@@ -420,59 +426,56 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -483,10 +486,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -524,71 +527,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -616,7 +619,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -639,11 +642,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -652,13 +655,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -668,7 +671,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -677,7 +680,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -686,7 +689,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -694,10 +697,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -762,27 +765,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="13.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="14.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>105</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -801,11 +800,11 @@
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>111</v>
       </c>
       <c r="C2" s="1">
@@ -824,11 +823,11 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>111</v>
       </c>
       <c r="C3" s="1">
@@ -847,15 +846,15 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>111</v>
       </c>
       <c r="C4" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -870,11 +869,11 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>111</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>112</v>
       </c>
       <c r="C5" s="1">
@@ -899,24 +898,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="18.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="22.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="16.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="21.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="21.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="18.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -926,253 +925,253 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
-        <v>0.0001</v>
+      <c r="B2" s="4">
+        <v>1E-4</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4">
         <v>0.75</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
-        <v>0.0002</v>
+      <c r="B3" s="4">
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="4">
         <v>0.75</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="5">
-        <v>0.0003</v>
+      <c r="B4" s="4">
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="4">
         <v>0.75</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
-        <v>0.0004</v>
+      <c r="B5" s="4">
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4">
         <v>0.75</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
-        <v>0.0005</v>
+      <c r="B6" s="4">
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4">
         <v>0.75</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
-        <v>0.001</v>
+      <c r="B7" s="4">
+        <v>1E-3</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="4">
         <v>0.8</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>0.8</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>0.004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="4">
         <v>0.9</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1182,57 +1181,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    </row>
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    </row>
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1240,68 +1224,57 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="7.147857142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="14.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>101</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1309,189 +1282,178 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="20.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="20.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" s="12">
-        <v>1.1</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C2" s="10">
         <v>1.2</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="10">
         <v>1.3</v>
       </c>
-      <c r="E2" s="12">
-        <v>0</v>
-      </c>
-      <c r="F2" s="12">
-        <v>0</v>
-      </c>
-      <c r="G2" s="12">
-        <v>0</v>
-      </c>
-      <c r="H2" s="12">
-        <v>0</v>
-      </c>
-      <c r="I2" s="12">
-        <v>0</v>
-      </c>
-      <c r="J2" s="12">
-        <v>0</v>
-      </c>
-      <c r="K2" s="12">
-        <v>0</v>
-      </c>
-      <c r="L2" s="12">
-        <v>0</v>
-      </c>
-      <c r="M2" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="E2" s="10">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0</v>
+      </c>
+      <c r="I2" s="10">
+        <v>0</v>
+      </c>
+      <c r="J2" s="10">
+        <v>0</v>
+      </c>
+      <c r="K2" s="10">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10">
+        <v>0</v>
+      </c>
+      <c r="M2" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" s="12">
-        <v>1</v>
-      </c>
-      <c r="C3" s="12">
-        <v>1</v>
-      </c>
-      <c r="D3" s="12">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12">
-        <v>0</v>
-      </c>
-      <c r="F3" s="12">
-        <v>0</v>
-      </c>
-      <c r="G3" s="12">
-        <v>0</v>
-      </c>
-      <c r="H3" s="12">
-        <v>0</v>
-      </c>
-      <c r="I3" s="12">
-        <v>0</v>
-      </c>
-      <c r="J3" s="12">
-        <v>0</v>
-      </c>
-      <c r="K3" s="12">
-        <v>0</v>
-      </c>
-      <c r="L3" s="12">
-        <v>0</v>
-      </c>
-      <c r="M3" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="B3" s="10">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>0</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="12">
-        <v>1</v>
-      </c>
-      <c r="C4" s="12">
-        <v>1</v>
-      </c>
-      <c r="D4" s="12">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12">
-        <v>5e-9</v>
-      </c>
-      <c r="F4" s="12">
-        <v>5e-9</v>
-      </c>
-      <c r="G4" s="12">
-        <v>5e-9</v>
-      </c>
-      <c r="H4" s="12">
-        <v>0</v>
-      </c>
-      <c r="I4" s="12">
-        <v>0</v>
-      </c>
-      <c r="J4" s="12">
-        <v>0</v>
-      </c>
-      <c r="K4" s="12">
-        <v>0</v>
-      </c>
-      <c r="L4" s="12">
-        <v>0</v>
-      </c>
-      <c r="M4" s="12">
+      <c r="B4" s="10">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="F4" s="10">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="G4" s="10">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1501,102 +1463,84 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="21.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="6" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="21.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1667,279 +1611,279 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="34.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="12">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="10">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="1">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="12">
-        <v>1e-10</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="10">
+        <v>1E-10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="12">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
+      <c r="B9" s="10">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="12">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
+      <c r="B12" s="10">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>39</v>
       </c>
       <c r="B14" s="1">
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="12">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3" t="s">
+      <c r="B15" s="10">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="12">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3" t="s">
+      <c r="B16" s="10">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>42</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>44</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>46</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>47</v>
       </c>
       <c r="B22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>48</v>
       </c>
       <c r="B23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>49</v>
       </c>
       <c r="B24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>50</v>
       </c>
       <c r="B25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>51</v>
       </c>
       <c r="B26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>52</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>55</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>56</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>57</v>
       </c>
       <c r="B32" s="1">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="12">
-        <v>0.000001</v>
+      <c r="B33" s="10">
+        <v>9.9999999999999995E-7</v>
       </c>
     </row>
   </sheetData>
@@ -1948,75 +1892,75 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="23.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="12">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
+    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1">
@@ -2029,78 +1973,70 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="11.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="15.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="10"/>
-      <c r="B2" s="3"/>
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="10"/>
-      <c r="B3" s="3"/>
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="10"/>
-      <c r="B4" s="3"/>
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="10"/>
-      <c r="B5" s="3"/>
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="10"/>
-      <c r="B6" s="3"/>
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="10"/>
-      <c r="B7" s="3"/>
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="10"/>
-      <c r="B8" s="3"/>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="10"/>
-      <c r="B9" s="3"/>
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
@@ -2110,108 +2046,95 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="16.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="17.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="12.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="16.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="3"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="3"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="3"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="3"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="3"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="3"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="3"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="3"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="3"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>

--- a/tests/ITER_coil_inf_3D/input_template.xlsx
+++ b/tests/ITER_coil_inf_3D/input_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APEC-M\tests\ITER_coil_inf_3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A99B08-2FDA-4329-A8D0-F97A86FA32A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0039FBA-CABD-4536-A1ED-12AE8801A795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="element_types" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="114">
   <si>
     <t>time_step_number</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>INFIN111</t>
+  </si>
+  <si>
+    <t>CURR</t>
   </si>
 </sst>
 </file>
@@ -426,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -462,6 +465,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1467,7 +1476,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="5" bestFit="1" customWidth="1"/>
@@ -1475,7 +1484,7 @@
     <col min="14" max="21" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>59</v>
       </c>
@@ -1539,8 +1548,11 @@
       <c r="U1" s="12" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V1" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1602,6 +1614,9 @@
         <v>0</v>
       </c>
       <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="14">
         <v>0</v>
       </c>
     </row>

--- a/tests/ITER_coil_inf_3D/input_template.xlsx
+++ b/tests/ITER_coil_inf_3D/input_template.xlsx
@@ -1,35 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APEC-M\tests\ITER_coil_inf_3D\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0039FBA-CABD-4536-A1ED-12AE8801A795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="element_types" sheetId="1" r:id="rId1"/>
-    <sheet name="cp" sheetId="2" r:id="rId2"/>
-    <sheet name="cpcyc" sheetId="3" r:id="rId3"/>
-    <sheet name="materials" sheetId="4" r:id="rId4"/>
-    <sheet name="real_constants" sheetId="5" r:id="rId5"/>
-    <sheet name="solver_settings" sheetId="6" r:id="rId6"/>
-    <sheet name="time_parameters" sheetId="7" r:id="rId7"/>
-    <sheet name="elem" sheetId="8" r:id="rId8"/>
-    <sheet name="node" sheetId="9" r:id="rId9"/>
-    <sheet name="transient_analysis" sheetId="10" r:id="rId10"/>
+    <sheet r:id="rId1" sheetId="1" name="element_types"/>
+    <sheet r:id="rId2" sheetId="2" name="cp"/>
+    <sheet r:id="rId3" sheetId="3" name="cpcyc"/>
+    <sheet r:id="rId4" sheetId="4" name="materials"/>
+    <sheet r:id="rId5" sheetId="5" name="real_constants"/>
+    <sheet r:id="rId6" sheetId="6" name="solver_settings"/>
+    <sheet r:id="rId7" sheetId="7" name="time_parameters"/>
+    <sheet r:id="rId8" sheetId="8" name="elem"/>
+    <sheet r:id="rId9" sheetId="9" name="node"/>
+    <sheet r:id="rId10" sheetId="10" name="transient_analysis"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="113">
   <si>
     <t>time_step_number</t>
   </si>
@@ -271,6 +265,9 @@
     <t>CPSIGN</t>
   </si>
   <si>
+    <t>CURR</t>
+  </si>
+  <si>
     <t>ansys_material_type</t>
   </si>
   <si>
@@ -365,23 +362,17 @@
   </si>
   <si>
     <t>SOLID97</t>
-  </si>
-  <si>
-    <t>INFIN111</t>
-  </si>
-  <si>
-    <t>CURR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,12 +383,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -429,62 +414,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="13">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -495,10 +471,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -536,71 +512,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -628,7 +604,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -651,11 +627,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -664,13 +640,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -680,7 +656,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -689,7 +665,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -698,7 +674,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -706,10 +682,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -774,47 +750,51 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="5" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="14.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" t="s">
         <v>105</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
-        <v>111</v>
+      <c r="B2" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
@@ -832,12 +812,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
-        <v>111</v>
+      <c r="B3" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
@@ -855,12 +835,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
-        <v>111</v>
+      <c r="B4" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="C4" s="1">
         <v>5</v>
@@ -875,29 +855,6 @@
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>111</v>
-      </c>
-      <c r="B5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -907,24 +864,24 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="5" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="22.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="16.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="21.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="21.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -934,253 +891,253 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="4">
         <v>0.75</v>
       </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="4">
         <v>0.75</v>
       </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="C4" s="1">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="4">
         <v>0.75</v>
       </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>4.0000000000000002E-4</v>
+        <v>0.0004</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="4">
         <v>0.75</v>
       </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>5.0000000000000001E-4</v>
+        <v>0.0005</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="4">
         <v>0.75</v>
       </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="G6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
       </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="G7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F8" s="4">
         <v>0.8</v>
       </c>
-      <c r="G8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="G8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="4">
         <v>0.8</v>
       </c>
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="4">
         <v>0.9</v>
       </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="G10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1190,42 +1147,57 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1233,57 +1205,68 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="14.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="7.147857142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I1" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J1" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
       <c r="C2" s="4"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1291,178 +1274,189 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="5" width="20.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="L1" s="11" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1">
         <v>21</v>
       </c>
-      <c r="B2" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C2" s="10">
+      <c r="B2" s="11">
+        <v>1.1</v>
+      </c>
+      <c r="C2" s="11">
         <v>1.2</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="11">
         <v>1.3</v>
       </c>
-      <c r="E2" s="10">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10">
-        <v>0</v>
-      </c>
-      <c r="I2" s="10">
-        <v>0</v>
-      </c>
-      <c r="J2" s="10">
-        <v>0</v>
-      </c>
-      <c r="K2" s="10">
-        <v>0</v>
-      </c>
-      <c r="L2" s="10">
-        <v>0</v>
-      </c>
-      <c r="M2" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="11">
+        <v>0</v>
+      </c>
+      <c r="F2" s="11">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11">
+        <v>0</v>
+      </c>
+      <c r="K2" s="11">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11">
+        <v>0</v>
+      </c>
+      <c r="M2" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1">
         <v>23</v>
       </c>
-      <c r="B3" s="10">
-        <v>1</v>
-      </c>
-      <c r="C3" s="10">
-        <v>1</v>
-      </c>
-      <c r="D3" s="10">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="10">
-        <v>0</v>
-      </c>
-      <c r="J3" s="10">
-        <v>0</v>
-      </c>
-      <c r="K3" s="10">
-        <v>0</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="11">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11">
+        <v>0</v>
+      </c>
+      <c r="K3" s="11">
+        <v>0</v>
+      </c>
+      <c r="L3" s="11">
+        <v>0</v>
+      </c>
+      <c r="M3" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>24</v>
       </c>
-      <c r="B4" s="10">
-        <v>1</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1</v>
-      </c>
-      <c r="D4" s="10">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10">
-        <v>5.0000000000000001E-9</v>
-      </c>
-      <c r="F4" s="10">
-        <v>5.0000000000000001E-9</v>
-      </c>
-      <c r="G4" s="10">
-        <v>5.0000000000000001E-9</v>
-      </c>
-      <c r="H4" s="10">
-        <v>0</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0</v>
-      </c>
-      <c r="J4" s="10">
-        <v>0</v>
-      </c>
-      <c r="K4" s="10">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10">
-        <v>0</v>
-      </c>
-      <c r="M4" s="10">
+      <c r="B4" s="11">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11">
+        <v>1</v>
+      </c>
+      <c r="D4" s="11">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11">
+        <v>5e-9</v>
+      </c>
+      <c r="F4" s="11">
+        <v>5e-9</v>
+      </c>
+      <c r="G4" s="11">
+        <v>5e-9</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0</v>
+      </c>
+      <c r="J4" s="11">
+        <v>0</v>
+      </c>
+      <c r="K4" s="11">
+        <v>0</v>
+      </c>
+      <c r="L4" s="11">
+        <v>0</v>
+      </c>
+      <c r="M4" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1472,87 +1466,106 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="5" width="21.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="5" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="S1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="T1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="V1" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1616,7 +1629,7 @@
       <c r="U2" s="1">
         <v>0</v>
       </c>
-      <c r="V2" s="14">
+      <c r="V2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1626,279 +1639,279 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="34.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="12" width="12.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="10">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B4" s="11">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="10">
-        <v>1E-10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B6" s="11">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="10">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B9" s="11">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="10">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B12" s="11">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B14" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="10">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B15" s="11">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="10">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B16" s="11">
+        <v>0.000001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B19" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B21" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B22" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B24" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B26" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B27" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B32" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="10">
-        <v>9.9999999999999995E-7</v>
+      <c r="B33" s="11">
+        <v>0.000001</v>
       </c>
     </row>
   </sheetData>
@@ -1907,75 +1920,75 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="23.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="11.290714285714287" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="10">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1">
@@ -1988,70 +2001,78 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="11.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="9"/>
+      <c r="B2" s="3"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="9"/>
+      <c r="B3" s="3"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="9"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="9"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="9"/>
+      <c r="B6" s="3"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="9"/>
+      <c r="B7" s="3"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="9"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="9"/>
+      <c r="B9" s="3"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
@@ -2061,95 +2082,108 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="10" width="16.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="17.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="12.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+      <c r="A1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1"/>
+      <c r="B6" s="3"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1"/>
+      <c r="B7" s="3"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1"/>
+      <c r="B9" s="3"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1"/>
+      <c r="B13" s="3"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1"/>
+      <c r="B14" s="3"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>

--- a/tests/ITER_coil_inf_3D/input_template.xlsx
+++ b/tests/ITER_coil_inf_3D/input_template.xlsx
@@ -670,22 +670,22 @@
         <v>1.3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1">
@@ -702,22 +702,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
@@ -743,13 +743,13 @@
         <v>5e-09</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tests/ITER_coil_inf_3D/input_template.xlsx
+++ b/tests/ITER_coil_inf_3D/input_template.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="element_types" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,28 +19,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000000"/>
-  </numFmts>
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,14 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -67,37 +47,13 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -176,34 +132,34 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="0000FF"/>
@@ -217,71 +173,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -305,53 +259,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -361,7 +316,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -370,7 +325,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -379,7 +334,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -387,10 +342,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -419,7 +374,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -432,12 +387,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -457,613 +413,539 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13.29071428571429" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="14.86214285714286" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="6" max="6"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TYPE_ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ELEMENT_TYPE</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>OPTION1</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>OPTION2</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>OPTION3</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>OPTION4</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>OPTION5</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="3" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>21</v>
       </c>
-      <c r="B2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>23</v>
       </c>
-      <c r="B3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>24</v>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20.14785714285714" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="6" max="6"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="7" max="7"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="8" max="8"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="9" max="9"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="5" min="10" max="10"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MATERIAL_ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MUR_X</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MUR_Y</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MUR_Z</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>RHO_X</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RHO_Y</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>RHO_Z</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>M_X</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>M_Y</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>M_Z</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="3" t="n">
+    <row r="2">
+      <c r="A2" t="n">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" t="n">
         <v>1.1</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="n">
         <v>1.2</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>1.3</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="3" t="n">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="3" t="n">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>5e-09</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" t="n">
         <v>5e-09</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" t="n">
         <v>5e-09</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21.14785714285714" bestFit="1" customWidth="1" style="7" min="1" max="1"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="2" max="2"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="5" max="5"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="6" max="6"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="7" max="7"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="8" max="8"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="9" max="9"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="10" max="10"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="11" max="11"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="12" max="12"/>
-    <col width="6.290714285714285" bestFit="1" customWidth="1" style="7" min="13" max="13"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="14" max="14"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="15" max="15"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="16" max="16"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="17" max="17"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="18" max="18"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="19" max="19"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="7" min="20" max="20"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CONSTANTS_ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>THK</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TURNS</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>VOL</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>RAD</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>T_X</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>T_Y</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>T_Z</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>V_X</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>V_Y</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>V_Z</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>OMEGA_X</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>OMEGA_Y</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>OMEGA_Z</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>LOC_X</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>LOC_Y</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>LOC_Z</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3" t="n">
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34.005" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="12.14785714285714" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SETTING</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ksp_type</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>preonly</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>pc_type</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>lu</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>initial_linear_tolerance</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
         <v>1e-06</v>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>max_linear_iterations</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>minimum_linear_tolerance</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="n">
         <v>1e-10</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1"/>
-    <row r="8" ht="18.75" customHeight="1"/>
-    <row r="9" ht="18.75" customHeight="1"/>
-    <row r="10" ht="18.75" customHeight="1"/>
-    <row r="11" ht="18.75" customHeight="1"/>
-    <row r="12" ht="18.75" customHeight="1"/>
-    <row r="13" ht="18.75" customHeight="1"/>
-    <row r="14" ht="18.75" customHeight="1"/>
-    <row r="15" ht="18.75" customHeight="1"/>
-    <row r="16" ht="18.75" customHeight="1"/>
-    <row r="17" ht="18.75" customHeight="1"/>
-    <row r="18" ht="18.75" customHeight="1"/>
-    <row r="19" ht="18.75" customHeight="1"/>
-    <row r="20" ht="18.75" customHeight="1"/>
-    <row r="21" ht="18.75" customHeight="1"/>
-    <row r="22" ht="18.75" customHeight="1"/>
-    <row r="23" ht="18.75" customHeight="1"/>
-    <row r="24" ht="18.75" customHeight="1"/>
-    <row r="25" ht="18.75" customHeight="1"/>
-    <row r="26" ht="18.75" customHeight="1"/>
-    <row r="27" ht="18.75" customHeight="1"/>
-    <row r="28" ht="18.75" customHeight="1"/>
-    <row r="29" ht="18.75" customHeight="1"/>
-    <row r="30" ht="18.75" customHeight="1"/>
-    <row r="31" ht="18.75" customHeight="1"/>
-    <row r="32" ht="18.75" customHeight="1"/>
-    <row r="33" ht="18.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>